--- a/uploads/FW.xlsx
+++ b/uploads/FW.xlsx
@@ -5,31 +5,20 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\james.santos\Downloads\ELETRICA LB 18 09\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\james.santos\Documents\28-07\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F7860A8F-E015-4C35-B78C-E6DF3AF7AAE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F2CF8BC-ED01-4FA0-B83A-F6CF3D412581}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{A9DC6551-0242-46D9-9329-447E5EBC4155}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="152511"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
     </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
       <xlwcv:version setVersion="2"/>
@@ -39,432 +28,390 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="336" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="128">
+  <si>
+    <t>[ KO4829816 3079058651 ]  COMULTADOR ELETRICO IGUINICAO VOLKS</t>
+  </si>
+  <si>
+    <t>ELETRICA</t>
+  </si>
+  <si>
+    <t>UN</t>
+  </si>
+  <si>
+    <t>[ DNI4001 ]  SIRENE RE 12V UNIVERSAL</t>
+  </si>
+  <si>
+    <t>[ H724VTEM LBPHS ]  LAMPADA H7 24V 70W IMP</t>
+  </si>
+  <si>
+    <t>[ OS64215TEM LB ]  LAMPADA H7 24V 70W OSRAM</t>
+  </si>
+  <si>
+    <t>[ ETE7343 ]  SOQUETE FAROL DIANT OPTICO UNIVERSAL</t>
+  </si>
+  <si>
+    <t>[ SLW848S FKF1048W ]  FAROL DE MILHA QUADRADO AUX 16LEDS 12/24V</t>
+  </si>
+  <si>
+    <t>[ 3373 ]  LAMPADA FAROL H4 12V</t>
+  </si>
+  <si>
+    <t>[ 24065 ELT1020 HK1020 ]  FUZIVEL LAMINA 20 AMP</t>
+  </si>
+  <si>
+    <t>[ GL1141 ]  LAMPADA 1141 12V "GE"</t>
+  </si>
+  <si>
+    <t>[ ME3014 TBF1004 04454 ]  TERMINAL BATERIA REFORCADO</t>
+  </si>
+  <si>
+    <t>[ 28222 GL46H4 ]  LAMPADA H4 24V 75/70W BIODO</t>
+  </si>
+  <si>
+    <t>[ BC043 GAB1005 ]  BUZINA AR ELETRICA 12V 2 CORNETAS C VALVULA</t>
+  </si>
+  <si>
+    <t>[ PL06081941 ]  LANTERNA UNIV C LED BASE RETA FACHI AMAR</t>
+  </si>
+  <si>
+    <t>[ PL06841961 ]  LANTERNA LAT C HAST ACRIL LED AMARELA C/ CONEC</t>
+  </si>
+  <si>
+    <t>[ GL069 ]  LAMPADA 69 12V 4W</t>
+  </si>
+  <si>
+    <t>[ DM01170 ]  RELOGIO TEMPERATURA AGUA MB 4MTS 60MM</t>
+  </si>
+  <si>
+    <t>[ ETE7665 ]  CHICOTE ADAPTACAO REDONDO 7VIAS</t>
+  </si>
+  <si>
+    <t>[ 10021123 ]  CHAVE SETA 1938 ATEGO AXOR ACTRO ATRON O500 2000 2012</t>
+  </si>
+  <si>
+    <t>[ ETE7664 CHW04019 ]  CHICOTE SENSOR PRESSAO ELETRICO 4 VIAS FEMEA</t>
+  </si>
+  <si>
+    <t>[ MTE4208 2T2919501 /  ]  SENSOR TEMPERATURA CUMMINS SERIE B F350</t>
+  </si>
+  <si>
+    <t>[ 30BD40DF2 ]  ROLAMENTO POLIA ALTERNADOR MB OM904 926 457</t>
+  </si>
+  <si>
+    <t>[ NF302 LD ]  FAROL AUXILIAR MILHA LD VOLVO FH13 2008.. ORIGINAL</t>
+  </si>
+  <si>
+    <t>NINO</t>
+  </si>
+  <si>
+    <t>[ 54451 OGV148LE ]  FAROL VOLVO VM LE 2005.. RETANGULAR</t>
+  </si>
+  <si>
+    <t>[ ETE5130 ]  CHICOTE CONECTOR 2 VIAS SENSOR SEGURANCA</t>
+  </si>
+  <si>
+    <t>[ 3RHO3348 3348 3RHO33 ]  SENSOR PRESSAO OLEO CARGO 1317E 1517E2422E 2428E VOLKS</t>
+  </si>
+  <si>
+    <t>[ 82114500 L1060  ]  LANTERNA SETA DIANT LD LED VOLVO FH 2010 A 2014</t>
+  </si>
+  <si>
+    <t>[ FT1092LD ]  LENTE FAROL SCANIA 124 SERIE 5 LD</t>
+  </si>
+  <si>
+    <t>[ FLXPC162 26 ]  PALHETA LIMPADOR VOLVO FH 26'' GANCHO</t>
+  </si>
+  <si>
+    <t>[ HL71150 ]  FUZIVEL 150 AMP MIDI DOURADO REFORÇADO</t>
+  </si>
+  <si>
+    <t>[ ETE7595 CHW05006 ]  CHICOTE CONECTOR 5 VIAS PORTA RELE</t>
+  </si>
+  <si>
+    <t>[ 3931064 384545  A384 ]  BOTAO DE ABRIR VIDRO ELETRICO MB1935 1630 24V ONIBUS</t>
+  </si>
+  <si>
+    <t>[ PL04822247 ]  LANTERNA MARMITAO FORD VW C VIGIA LED MOD NOVO</t>
+  </si>
+  <si>
+    <t>[ UF11474 ]  PORTA ESCOVA MOTOR PARTIDA MITSUBISHI FORD MAN CATERPILLAR 24V</t>
+  </si>
+  <si>
+    <t>[ PL04832107 ]  LENTE CR LANTERNA TRASEIRA VW CONSTELLATION DELIVERY CARGO</t>
+  </si>
+  <si>
+    <t>[ LCG1141 3079058652 ]  COMUTADOR IGNICAO VW WORK CONST DELIVERY</t>
+  </si>
+  <si>
+    <t>[ 3RHO5599 20493673 40 ]  INTERRUPTOR PNEUMATICO VOLVO VM</t>
+  </si>
+  <si>
+    <t>[ DNI0125 ]  RELE AUXILIAR MINI 12V 40A 4 TERMINAIS VW CAMINHAO E ONIBUS</t>
+  </si>
+  <si>
+    <t>[ IMB101322624 1013226 ]  ELETROVENTILADOR EXAUSTOR CUPULA ONIBUS VOLKS VOLARE 24V</t>
+  </si>
+  <si>
+    <t>[ P20KNR2 M201A ]  CHAVE SELETORA 22MM 2 POSICAO C CHAVE</t>
+  </si>
+  <si>
+    <t>[ MLT0800004 ETE7684 ]  CHICOTE CONECTOR 3 VIAS MB ONIBUS</t>
+  </si>
+  <si>
+    <t>[ 6202NSE ]  ROLAMENTO 6202 MANCAL ALTERNADOR UNO VIVACE 2011 LOJA</t>
+  </si>
+  <si>
+    <t>NSK</t>
+  </si>
+  <si>
+    <t>[ TC3066 ETE5477 ]  CONECTOR 3 VIAS SENSOR ROTACAO MB AXOR</t>
+  </si>
+  <si>
+    <t>[ DR45012VLP FO0031319 ]  AUTOMATICO AUXILIAR RELE MOTOR PARTIDA 24V MAN TGX 28440</t>
+  </si>
+  <si>
+    <t>[ Z35012 ]  MOTOR PARTIDA MAN 10180 10240 VW 17280</t>
+  </si>
+  <si>
+    <t>[ FLX251620LD PL16204127 ]  LANTERNA TRAS LD DAF XF</t>
+  </si>
+  <si>
+    <t>FLX</t>
+  </si>
+  <si>
+    <t>[ LFLX 1034 24V 3141 L ]  LAMPADA 1034 24V 2 POLOS 12 LEDS</t>
+  </si>
+  <si>
+    <t>[ FLX25.0706AMARELA ]  LANTERNA TAPA SOL VOLVO FH NH AMARELA</t>
+  </si>
+  <si>
+    <t>[ FLXCH85323 ETE5323 R ]  CHICOTE 8 VIAS REPARO DOSADOR ARLA MB ACCELO 1016</t>
+  </si>
+  <si>
+    <t>[ FLXML9308 9390453024 ]  MOTOR LIMPADOR PARABRISA MB 352 24V</t>
+  </si>
+  <si>
+    <t>[ FLXIT34271 DNI2407 6 ]  INTERRUPTOR VIDRO ELETRICO DUPLO VOLKS</t>
+  </si>
+  <si>
+    <t>[ FLXL069 12V LED ]  LAMPADA LED 69 12V 8 LEDS</t>
+  </si>
+  <si>
+    <t>[ LFLX2880 12V ]  LAMPADA 2880 12V LED</t>
+  </si>
+  <si>
+    <t>[ FLX6411 12V LED ]  LAMPADA 6411 TORPEDO 12V 8 LEDS</t>
+  </si>
+  <si>
+    <t>[ FLX6418 12V LED ]  LAMPADA 6418 TORPEDO 12V 8 LEDS</t>
+  </si>
+  <si>
+    <t>[ FLXCH47664 ETE7664 C ]  CHICOTE SENSOR PRESSAO ELETRICO 4 VIAS FEMEA IVECO MB SCANIA VW VOLVO</t>
+  </si>
+  <si>
+    <t>[ FLXCH35102 ETE5102 ]  CHICOTE 3 VIAS SENSOR ROTACAO VW GOL FOX GOLF POLO PARATI UP</t>
+  </si>
+  <si>
+    <t>MT</t>
+  </si>
+  <si>
+    <t>[ FLXCH35563 ETE5563 ]  CHICOTE 3 VIAS REPARO AMAROK GOL FOX VOYAGE JETTA</t>
+  </si>
+  <si>
+    <t>[ FLXCH35322 ETE5322 ]  CHICOTE 3 VIAS SENSOR BORBOLETA E ROTACAO AMAROK GOLF JETTA POLO VOYAGE</t>
+  </si>
+  <si>
+    <t>[ FLXCH35900 ETE5900 ]  CHICOTE 2 VIAS FEMEA REPARO BICO INJETOR MB</t>
+  </si>
+  <si>
+    <t>[ FLXCH37752 3RHO7722 ETE7752 0071530828 ]  SENSOR PRESSAO OLEO MB ATEGO AXOR OM904/906</t>
+  </si>
+  <si>
+    <t>[ FLXCH35976 ETE5976 21418448 ]  CHICOTE 3 VIAS REPARO MODULO VOLVO VM 270 VW CONSTELLATION</t>
+  </si>
+  <si>
+    <t>[ FLXCH28731 ETE8731 ]  CONECTOR 2 VIAS REPARO BICO INJETOR VENTOINHA FIAT DUCATO</t>
+  </si>
+  <si>
+    <t>[ FLXCH27798 ETE7798 ]  CHICOTE 2 VIAS FEMEA CEBOLINHA RE VW GOLF/POLO</t>
+  </si>
+  <si>
+    <t>[ FLXCH27879 ETE7879 ]  CHICOTE 2 VIAS FEMEA BULIDOG</t>
+  </si>
+  <si>
+    <t>[ FLXCH27654 ETE7654 ]  CHICOTE 2 VIAS SENSOR ROTACAO LATERNA PLACA PEUGEOT 26 RENAULT CLIO SCENIC</t>
+  </si>
+  <si>
+    <t>[ FLXCH27732 ETE7732 ]  CHICOTE 2 VIAS BICO INJETOR TEMPERATURA GOL PARATI APOS 99</t>
+  </si>
+  <si>
+    <t>[ FLXCH24130 ETE4130 ]  CHICOTE 2 VIAS SENSOR CINTO SEGURANCA FORD 250 CAMINHAO ONIBUS</t>
+  </si>
+  <si>
+    <t>[ FLXCH15111 ETE5111 ]  CHICOTE ALTERNADOR 1 VIA FEMEA VOLKS</t>
+  </si>
+  <si>
+    <t>[ KT016800 337ST 00615 ]  KIT BUCHA COM ROLAMENTO 29MT MOTOR PARTIDA MB FORD DELCO VOLKS</t>
+  </si>
+  <si>
+    <t>[ CH27179 ETE7179 ]  CHICOTE 2 VIAS SENSOR VELOCIDADE LAMPADA H8 H9 H11 H16</t>
+  </si>
+  <si>
+    <t>3RHO</t>
+  </si>
+  <si>
+    <t>[ CS2X1RL25 ]  CABO 2X1MM COBRE PURO</t>
+  </si>
+  <si>
+    <t>[ CS50RL25 ]  CABO 50MM COBRE PURO</t>
+  </si>
+  <si>
+    <t>[  FLXAB5030 ]  ABRACADEIRA NYLON 30CM</t>
+  </si>
+  <si>
+    <t>[ FLXCH37741 ]  CHICOTE 3 VIAS SENSOR BORBOLETA FIAT FORD MB ACELO VW CONST</t>
+  </si>
+  <si>
+    <t>[ FLX251620LE PL16204227 ]  LANTERNA TRAS LE DAF XF</t>
+  </si>
+  <si>
+    <t>[ FLX251621LE 1914690 ]  LENTE LANTERNA TRAS LE DAF XF</t>
+  </si>
+  <si>
+    <t>[ FLX251621LD 1914691 ]  LENTE LANTERNA TRAS LD DAF XF</t>
+  </si>
+  <si>
+    <t>[ 4246MTE 55265789 ]  SENSOR NIVEL AGUA FIAT MOBI UNO ARGO CRONOS</t>
+  </si>
+  <si>
+    <t>[ ETE8531 ]  CHICOTE REPARO 2 VIAS UNIVERSAL</t>
+  </si>
+  <si>
+    <t>[ T070076 2W0919183E DS23715  ]  BOIA SENSOR COMBUSTIVEL VOLKS 14190 15210 15190 210L</t>
+  </si>
+  <si>
+    <t>TSA</t>
+  </si>
+  <si>
+    <t>[ GL130H11 ]  LAMPADA H11 24V 70W</t>
+  </si>
+  <si>
+    <t>Marca (Se for Marca Específica)</t>
+  </si>
+  <si>
+    <t>QTD</t>
+  </si>
   <si>
     <t>Descrição LBDIESEL</t>
   </si>
   <si>
-    <t>Marca (Se for Marca Específica)</t>
-  </si>
-  <si>
-    <t>UN</t>
-  </si>
-  <si>
-    <t>QTD</t>
-  </si>
-  <si>
-    <t>[ 146 ]  WHITE LUB SUPER PE AEROSOL 300ML  DESENGRIPANTE</t>
-  </si>
-  <si>
-    <t>SEMA - ORBI QUIMICA</t>
-  </si>
-  <si>
-    <t>car80</t>
-  </si>
-  <si>
-    <t>[ 5910 ]  VEDA ESCAPE 100GR</t>
-  </si>
-  <si>
-    <t>[ 337 ]  COLA SILICONE COLA MAIS PRETA</t>
-  </si>
-  <si>
-    <t>tenkbond</t>
-  </si>
-  <si>
-    <t>[ 4 ]  LOCTITE TRAVA ROSCA QUIMICA 10 GRAMAS</t>
-  </si>
-  <si>
-    <t>[ 1070405 208BENJA FLX ]  BOMBA D AGUA P CLIMATIZADOR 24V</t>
-  </si>
-  <si>
-    <t>ELETRICA</t>
+    <t>kostal</t>
+  </si>
+  <si>
+    <t>dni</t>
+  </si>
+  <si>
+    <t>ete</t>
+  </si>
+  <si>
+    <t>3rho</t>
+  </si>
+  <si>
+    <t>gauss</t>
+  </si>
+  <si>
+    <t>osram</t>
+  </si>
+  <si>
+    <t>tg</t>
+  </si>
+  <si>
+    <t>a.m.s</t>
+  </si>
+  <si>
+    <t>gaus</t>
+  </si>
+  <si>
+    <t>cinap</t>
+  </si>
+  <si>
+    <t>neolux</t>
   </si>
   <si>
     <t>vto</t>
   </si>
   <si>
-    <t>[ 7 ]  LIMPA CONTATO SPRAY 300ML</t>
-  </si>
-  <si>
-    <t>[ KO4829816 3079058651 ]  COMULTADOR ELETRICO IGUINICAO VOLKS</t>
-  </si>
-  <si>
-    <t>kostal</t>
-  </si>
-  <si>
-    <t>[ 8 ]  DESCARBONIZANTE CAR 2000 LIMPA BICO INJETOR</t>
-  </si>
-  <si>
-    <t>orbi ou tenkbond</t>
-  </si>
-  <si>
-    <t>[ H724VTEM LBPHS ]  LAMPADA H7 24V 70W IMP</t>
-  </si>
-  <si>
-    <t>[  ]  ABRACADEIRA NYLON 30CM</t>
-  </si>
-  <si>
-    <t>dni</t>
-  </si>
-  <si>
-    <t>[ 7415 3RHO400 ]  INTERRUPTOR FREIO VOLKS CONSTELLATION TODOS</t>
-  </si>
-  <si>
-    <t>marflex</t>
-  </si>
-  <si>
-    <t>[ IM34300 GEA2001 3934 ]  INTERRUPTOR VIDRO ELETRICO SIMPLES LD VOLKS TODOS</t>
+    <t>pradolux</t>
+  </si>
+  <si>
+    <t>turotest</t>
+  </si>
+  <si>
+    <t>ospina/marili/a</t>
+  </si>
+  <si>
+    <t>chw</t>
+  </si>
+  <si>
+    <t>m.t.e</t>
+  </si>
+  <si>
+    <t>nsk</t>
+  </si>
+  <si>
+    <t>nino</t>
+  </si>
+  <si>
+    <t>unifap</t>
+  </si>
+  <si>
+    <t>gf</t>
   </si>
   <si>
     <t>marilia</t>
   </si>
   <si>
-    <t>[ 001125 MB047 ]  RELOGIO TEMP RED MEC 2MT 40 100</t>
-  </si>
-  <si>
-    <t>WILLTEC - NUNE</t>
-  </si>
-  <si>
-    <t>wiltec</t>
-  </si>
-  <si>
-    <t>[ FLX1046 ]  FAROL DE MILHA REDONDO AUX 14LEDS 12/24V</t>
-  </si>
-  <si>
-    <t>tgpoli</t>
-  </si>
-  <si>
-    <t>[ 9006PRC1 ]  LAMPADA BIODO HB4 12V 55W GM S10 VW TODOS</t>
-  </si>
-  <si>
-    <t>tigeauto</t>
-  </si>
-  <si>
-    <t>[ ZM8589011 BZ1921 991 ]  BENDIX MITSUBISHI 20D VOLVO VW CONSTELLATION MAN</t>
+    <t>delco</t>
   </si>
   <si>
     <t>zen</t>
   </si>
   <si>
-    <t>[ TU300503 WI02051C 00 ]  RELOGIO PRESSAO OLEO 60MM SC111 112</t>
-  </si>
-  <si>
-    <t>turotest</t>
-  </si>
-  <si>
-    <t>[ 10182 ]  FITA ISOLANTE PRETA 10MTS</t>
-  </si>
-  <si>
-    <t>isorflex</t>
-  </si>
-  <si>
-    <t>[ IM11036 ]  BOTAO PARTIDA UNIVERSAL</t>
-  </si>
-  <si>
-    <t>[ 28222 GL46H4 ]  LAMPADA H4 24V 75/70W BIODO</t>
-  </si>
-  <si>
-    <t>hella</t>
-  </si>
-  <si>
-    <t>[ 12X300 ]  LIMPA CONTATO SPRAY 300ML</t>
-  </si>
-  <si>
-    <t>[ PL06841961 ]  LANTERNA LAT C HAST ACRIL LED AMARELA C/ CONEC</t>
-  </si>
-  <si>
-    <t>pradolux</t>
-  </si>
-  <si>
-    <t>[ TJG941521 BF7T15520A ]  INTERRUPTOR LUZ RE CAMBIO EATON VOLKS FORD 91..</t>
-  </si>
-  <si>
-    <t>3RHO</t>
-  </si>
-  <si>
-    <t>3rh</t>
-  </si>
-  <si>
-    <t>[ 3507700 GS002 ]  TOMADA LUZ 7 POLOS REDONDA FEMEA</t>
-  </si>
-  <si>
-    <t>engatcar</t>
-  </si>
-  <si>
-    <t>[ LP13MM MMV5213 ]  ESPAGUET CORRUGADO 13MM</t>
-  </si>
-  <si>
-    <t>dni metro</t>
-  </si>
-  <si>
-    <t>[ DANI0240 D09309 ]  RELE AUX UNIV 24V 10/20A SCANI MB1933 2635 O400</t>
-  </si>
-  <si>
-    <t>[ ELT1015 ]  FUZIVEL LAMINA 15 AMPERES UNIDADE</t>
-  </si>
-  <si>
-    <t>[  LI194 12V  TK0912 G ]  LAMPADA PINGAO 194 12V 3W</t>
-  </si>
-  <si>
-    <t>neolux</t>
-  </si>
-  <si>
-    <t>[ ZEN0105 BZM0105 B200 ]  BENDIX PARTIDA VW CARGO MB TRATOR JF CBT</t>
-  </si>
-  <si>
-    <t>BOSCH</t>
-  </si>
-  <si>
-    <t>bosch</t>
-  </si>
-  <si>
-    <t>[ ETE7731 ]  CONECTOR 1 POLO 2VIAS UNIVERSA C RABICHO</t>
-  </si>
-  <si>
-    <t>ete</t>
-  </si>
-  <si>
-    <t>[ IV83327 AMX20327 ]  INDUZIDO PARTIDA JF 12V MB</t>
-  </si>
-  <si>
-    <t>[ FT479 ]  FAROL MILHA LE MB AXOR 1938</t>
-  </si>
-  <si>
-    <t>[ PL07281409 ]  LANTERNA TRAS VV VOLVO FH MODERNO LE</t>
-  </si>
-  <si>
-    <t>PRADOLUX</t>
-  </si>
-  <si>
-    <t>[ PL07281309 ]  LANTERNA TRAS VV VOLVO FH MODERNO LD</t>
-  </si>
-  <si>
-    <t>ptadolux</t>
-  </si>
-  <si>
-    <t>[ 3RHO6634 EC7619 2V59 ]  INTERRUPTOR TRANSFERENCIA FORD MAN MB VW IVECO</t>
-  </si>
-  <si>
-    <t>[ 18621 ]  COLA PARABRISA PU 55 230ML 380G</t>
-  </si>
-  <si>
-    <t>[ 3RHO6616 RH6616 ]  INTERRUPTOR TRANSF STRALIS VOLKS CONSTELAT 18310..</t>
-  </si>
-  <si>
-    <t>3rho</t>
-  </si>
-  <si>
-    <t>[  ]  COLA TRAVA PARAFUSO 10GR VERMELHO</t>
-  </si>
-  <si>
-    <t>[ MMR1013 DNI0122 ]  RELE AUXILIAR 70A 12V UNIVERSAL</t>
-  </si>
-  <si>
-    <t>[ IM11347  DNI0216 ]  RELE AUXILIAR 24V 5 TERMINAIS</t>
-  </si>
-  <si>
-    <t>[ 54451 OGV148LE ]  FAROL VOLVO VM LE 2005.. RETANGULAR</t>
-  </si>
-  <si>
-    <t>[ ETE7687 CH27687 ]  CHICOTE ELETRICO 2 VIAS REDONDO MB VW SCANIA</t>
-  </si>
-  <si>
-    <t>[ NF354 LD ]  FAROL DIANT LD MB ATEGO ORIGINAL 2013..</t>
-  </si>
-  <si>
-    <t>nino</t>
-  </si>
-  <si>
-    <t>[ 18746 ]  TINTA SPRAY PRETO FOSCO 340ML</t>
-  </si>
-  <si>
-    <t>[ HL71150 ]  FUZIVEL 150 AMP MIDI DOURADO REFORÇADO</t>
-  </si>
-  <si>
-    <t>[ 64038 HFX4,0AZ ]  FIO 4.00MM AZUL</t>
-  </si>
-  <si>
-    <t>MT</t>
-  </si>
-  <si>
-    <t>preto dni</t>
-  </si>
-  <si>
-    <t>[ DNI5255 LP7,5MM ]  ESPAGUETE CORRUGADO 7.5MM</t>
-  </si>
-  <si>
-    <t>[ DNI5023 FLX705023 ]  FITA ISOLANTE DE TECIDO COM ADERENCIA 10MTS</t>
-  </si>
-  <si>
-    <t>[ PL04822247 ]  LANTERNA MARMITAO FORD VW C VIGIA LED MOD NOVO</t>
-  </si>
-  <si>
-    <t>prado lux</t>
-  </si>
-  <si>
-    <t>[ PL07622463 PL0762006 ]  LANTERNA TRAS 10LEDS 24V AM 125MM MB BICUDO FACHINI ONIBUS</t>
-  </si>
-  <si>
-    <t>[ TB0917 ]  SPRAY PRETO FOSCO 350ML</t>
-  </si>
-  <si>
-    <t>[ GA041 ]  REGULADOR ALTERN MB VOLVO VW ONIBUS 24V 28V 140A</t>
-  </si>
-  <si>
-    <t>gauss</t>
-  </si>
-  <si>
-    <t>[  ]  PARAFUSO 4MM P LANTERNA</t>
-  </si>
-  <si>
-    <t>MDZ</t>
-  </si>
-  <si>
-    <t>[ GA121 IK5121 ]  REGULADOR VOLTAGEM PUNTO PALIO CORSA</t>
-  </si>
-  <si>
-    <t>[ UF11474 ]  PORTA ESCOVA MOTOR PARTIDA MITSUBISHI FORD MAN CATERPILLAR 24V</t>
-  </si>
-  <si>
-    <t>unifap</t>
-  </si>
-  <si>
-    <t>[ 6303DDUC3 GAR6303 18 ]  ROLAMENTO ALTERNADOR BLINDADO</t>
-  </si>
-  <si>
-    <t>GAUSS</t>
-  </si>
-  <si>
-    <t>ikro</t>
-  </si>
-  <si>
-    <t>[ PL04832107 ]  LENTE CR LANTERNA TRASEIRA VW CONSTELLATION DELIVERY CARGO</t>
-  </si>
-  <si>
-    <t>[ ASXH8 ]  LAMPADA FAROL H8 12V 35W USO GERAL</t>
-  </si>
-  <si>
-    <t>[  5544 P4046 3R3346 ]  INTERRUPTOR PRESSAO OLEO FIAT PALIO STRADA FIORINO UNO SIENA PUNTO</t>
-  </si>
-  <si>
-    <t>[ DNI2160 K4052360 IM5 ]  CHAVE DE LUZ 24V C REOSTATO VOLKS CONSTELLATION 2000 EM DIANTE 24V</t>
-  </si>
-  <si>
-    <t>[ MDAG001 ]  AGUA DESMINERALIZADA 1L</t>
-  </si>
-  <si>
-    <t>[ IMB101322624 1013226 ]  ELETROVENTILADOR EXAUSTOR CUPULA ONIBUS VOLKS VOLARE 24V</t>
-  </si>
-  <si>
-    <t>[ GL31HB3 ]  LAMPADA FAROL HB24 12V 60W</t>
-  </si>
-  <si>
-    <t>[ GL35HB4 NEO9006 ]  LAMPADA FAROL HB4 12V</t>
-  </si>
-  <si>
-    <t>[ PL07962461 ]  LANTERNA TRASEIRA 10LEDS 24V AMARELA</t>
-  </si>
-  <si>
-    <t>[ DR45012VLP FO0031319 ]  AUTOMATICO AUXILIAR RELE MOTOR PARTIDA 24V MAN TGX 28440</t>
-  </si>
-  <si>
-    <t>delco</t>
-  </si>
-  <si>
-    <t>[ FLX251001LE PL048222 ]  LANTERNA MARMITAO FORD VW C VIGIA LED</t>
-  </si>
-  <si>
-    <t>FLX</t>
-  </si>
-  <si>
-    <t>[ 3RHO6636 2S0941503 ]  INTERRUPTOR TRANSFERENCIA VW CONSTELLATION 13190 15190</t>
-  </si>
-  <si>
-    <t>rho</t>
-  </si>
-  <si>
-    <t>[ FLXML9002 F006B20021 ]  MOTOR LIMPADOR PARABRISA 24V AGRALE VOLKS WORKER CONST</t>
-  </si>
-  <si>
-    <t>euro</t>
-  </si>
-  <si>
-    <t>[ FLXML9308 9390453024 ]  MOTOR LIMPADOR PARABRISA MB 352 24V</t>
-  </si>
-  <si>
-    <t>[ FLXIT34271 DNI2407 6 ]  INTERRUPTOR VIDRO ELETRICO DUPLO VOLKS</t>
+    <t>ew</t>
   </si>
   <si>
     <t>dial</t>
   </si>
   <si>
-    <t>[ FLXCH29731 ETE9731 C ]  CHICOTE ELETRICO 2VIAS BICO INJETOR CONTRAPECA 7731</t>
-  </si>
-  <si>
-    <t>[ FLXCH35976 ETE5976 21418448 ]  CHICOTE 3 VIAS REPARO MODULO VOLVO VM 270 VW CONSTELLATION</t>
-  </si>
-  <si>
-    <t>[ FLXCH28731 ETE8731 ]  CONECTOR 2 VIAS REPARO BICO INJETOR VENTOINHA FIAT DUCATO</t>
-  </si>
-  <si>
-    <t>[ FLXCH29130 ETE9130 ]  CHICOTE 2 VIAS SENSOR CINTO SEGURANCA FORD F250 VW CAMINHAO ONIBUS</t>
-  </si>
-  <si>
-    <t>[ FLXCH27654 ETE7654 ]  CHICOTE 2 VIAS SENSOR ROTACAO LATERNA PLACA PEUGEOT 26 RENAULT CLIO SCENIC</t>
-  </si>
-  <si>
-    <t>[ FLXCH27731 ETE7731 ]  CONECTOR 1 POLO 2VIAS UNIVERSA C RABICHO MB 1620 710 VW CONSTELLATION</t>
-  </si>
-  <si>
-    <t>[ FLXCH27687 ETE7687 CH27687 ]  CHICOTE ELETRICO 2 VIAS REDONDO MB VW SCANIA</t>
-  </si>
-  <si>
-    <t>[ FLXCH24130 ETE4130 ]  CHICOTE 2 VIAS SENSOR CINTO SEGURANCA FORD 250 CAMINHAO ONIBUS</t>
-  </si>
-  <si>
-    <t>[ FLXCH15111 ETE5111 ]  CHICOTE ALTERNADOR 1 VIA FEMEA VOLKS</t>
-  </si>
-  <si>
-    <t>[ KT016800 337ST 00615 ]  KIT BUCHA COM ROLAMENTO 29MT MOTOR PARTIDA MB FORD DELCO VOLKS</t>
+    <t xml:space="preserve">nlt cx </t>
+  </si>
+  <si>
+    <t>par  autopoli</t>
   </si>
   <si>
     <t>war</t>
   </si>
   <si>
-    <t>[ 3RHO3348 3348 3RHO33 ]  SENSOR PRESSAO OLEO CARGO 1317E 1517E2422E 2428E VOLKS</t>
-  </si>
-  <si>
-    <t>[ SD150MMPR ]  FIO 1,5MM COBRE PURO</t>
-  </si>
-  <si>
-    <t>dni100 metro</t>
-  </si>
-  <si>
-    <t>[ 4246MTE 55265789 ]  SENSOR NIVEL AGUA FIAT MOBI UNO ARGO CRONOS</t>
-  </si>
-  <si>
-    <t>[ ETE8531 ]  CHICOTE REPARO 2 VIAS UNIVERSAL</t>
-  </si>
-  <si>
-    <t>[ T070076 2W0919183E DS23715  ]  BOIA SENSOR COMBUSTIVEL VOLKS 14190 15210 15190 210L</t>
-  </si>
-  <si>
-    <t>TSA</t>
-  </si>
-  <si>
-    <t>tsa</t>
-  </si>
-  <si>
-    <t>[ FLXCH35837 ETE5837 ]  CHICOTE 3 VIAS CAIXA DIRECAO ELETRICA CITROEN PEUGEOT RENAULT</t>
+    <t>25 metro</t>
+  </si>
+  <si>
+    <t>metro</t>
+  </si>
+  <si>
+    <t>idebras</t>
+  </si>
+  <si>
+    <t>shock</t>
+  </si>
+  <si>
+    <t>MARCA</t>
   </si>
   <si>
     <t>PREÇO</t>
   </si>
   <si>
-    <t>MARCA</t>
-  </si>
-  <si>
-    <t>codigo</t>
+    <t>CODIGO</t>
   </si>
 </sst>
 </file>
@@ -515,11 +462,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -853,230 +799,234 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2C3A35EB-4576-44A1-96B2-99C5537772D5}">
-  <dimension ref="A1:G88"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:G83"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.88671875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="94.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.21875" customWidth="1"/>
     <col min="4" max="4" width="3.5546875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="4.44140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="17.44140625" customWidth="1"/>
+    <col min="7" max="7" width="16.109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>141</v>
+        <v>127</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>0</v>
+        <v>91</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1</v>
+        <v>89</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>3</v>
+        <v>90</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>140</v>
+        <v>126</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
-        <v>1457</v>
+        <v>15396</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>2</v>
       </c>
       <c r="E2" s="1">
-        <v>50</v>
+        <v>2</v>
       </c>
       <c r="F2" s="1">
-        <v>8.39</v>
+        <v>26.79</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>6</v>
+        <v>92</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
-        <v>3248</v>
+        <v>16963</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>2</v>
       </c>
       <c r="E3" s="1">
-        <v>10</v>
-      </c>
-      <c r="F3" s="1"/>
-      <c r="G3" s="1"/>
+        <v>2</v>
+      </c>
+      <c r="F3" s="1">
+        <v>16.29</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>93</v>
+      </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
-        <v>4241</v>
+        <v>17551</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>2</v>
       </c>
       <c r="E4" s="1">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="F4" s="1">
-        <v>5.69</v>
+        <v>11.49</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>9</v>
+        <v>96</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
-        <v>4377</v>
+        <v>17562</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>2</v>
       </c>
       <c r="E5" s="1">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="F5" s="1">
-        <v>8.48</v>
+        <v>31.49</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>6</v>
+        <v>97</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
-        <v>5782</v>
+        <v>17655</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>2</v>
       </c>
       <c r="E6" s="1">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F6" s="1">
-        <v>14.89</v>
+        <v>10.130000000000001</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>13</v>
+        <v>94</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
-        <v>6298</v>
+        <v>29849</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>2</v>
       </c>
       <c r="E7" s="1">
-        <v>40</v>
+        <v>3</v>
       </c>
       <c r="F7" s="1">
-        <v>11.69</v>
+        <v>28.44</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>6</v>
+        <v>98</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
-        <v>15396</v>
+        <v>101283</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>2</v>
       </c>
       <c r="E8" s="1">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F8" s="1">
-        <v>27.88</v>
+        <v>8.2899999999999991</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>16</v>
+        <v>96</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
-        <v>16173</v>
+        <v>101349</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>2</v>
       </c>
       <c r="E9" s="1">
-        <v>13</v>
+        <v>80</v>
       </c>
       <c r="F9" s="1">
-        <v>15.19</v>
+        <v>0.38</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>18</v>
+        <v>99</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
-        <v>17551</v>
+        <v>102124</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>2</v>
@@ -1085,67 +1035,67 @@
         <v>10</v>
       </c>
       <c r="F10" s="1">
-        <v>7.35</v>
+        <v>1.19</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>13</v>
+        <v>100</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
-        <v>18286</v>
+        <v>103338</v>
       </c>
       <c r="B11" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E11" s="1">
         <v>20</v>
       </c>
-      <c r="C11" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="E11" s="1">
-        <v>200</v>
-      </c>
       <c r="F11" s="1">
-        <v>19.440000000000001</v>
+        <v>6.49</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>21</v>
+        <v>101</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
-        <v>18660</v>
+        <v>105841</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>2</v>
       </c>
       <c r="E12" s="1">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F12" s="1">
-        <v>55.22</v>
+        <v>14.69</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>23</v>
+        <v>102</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
-        <v>25701</v>
+        <v>113056</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>2</v>
@@ -1154,44 +1104,44 @@
         <v>1</v>
       </c>
       <c r="F13" s="1">
-        <v>16.5</v>
+        <v>88.99</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>25</v>
+        <v>103</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
-        <v>27687</v>
+        <v>115412</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>27</v>
+        <v>1</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>2</v>
       </c>
       <c r="E14" s="1">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="F14" s="1">
-        <v>136.55000000000001</v>
+        <v>17.489999999999998</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>28</v>
+        <v>104</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
-        <v>29590</v>
+        <v>115456</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>2</v>
@@ -1200,67 +1150,67 @@
         <v>10</v>
       </c>
       <c r="F15" s="1">
-        <v>27.88</v>
+        <v>23.99</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>30</v>
+        <v>104</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
-        <v>33535</v>
+        <v>116471</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>2</v>
       </c>
       <c r="E16" s="1">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="F16" s="1">
-        <v>11.69</v>
+        <v>1.0900000000000001</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>32</v>
+        <v>96</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
-        <v>35667</v>
+        <v>116602</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>2</v>
       </c>
       <c r="E17" s="1">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F17" s="1">
-        <v>242.44</v>
+        <v>163.44</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>34</v>
+        <v>105</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" s="1">
-        <v>101122</v>
+        <v>116848</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>2</v>
@@ -1269,44 +1219,44 @@
         <v>2</v>
       </c>
       <c r="F18" s="1">
-        <v>134.55000000000001</v>
+        <v>23.89</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>36</v>
+        <v>94</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
-        <v>101699</v>
+        <v>116985</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>37</v>
+        <v>19</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>2</v>
       </c>
       <c r="E19" s="1">
-        <v>100</v>
+        <v>4</v>
       </c>
       <c r="F19" s="1">
-        <v>2.6</v>
+        <v>243.12</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>38</v>
+        <v>106</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" s="1">
-        <v>103315</v>
+        <v>119049</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>39</v>
+        <v>20</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>2</v>
@@ -1315,86 +1265,90 @@
         <v>2</v>
       </c>
       <c r="F20" s="1">
-        <v>9.89</v>
+        <v>20.190000000000001</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>25</v>
+        <v>107</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" s="1">
-        <v>105841</v>
+        <v>120539</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>2</v>
       </c>
       <c r="E21" s="1">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="F21" s="1">
-        <v>13.99</v>
+        <v>119.99</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>41</v>
+        <v>108</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" s="1">
-        <v>111626</v>
+        <v>120713</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>2</v>
       </c>
       <c r="E22" s="1">
-        <v>30</v>
-      </c>
-      <c r="F22" s="1"/>
-      <c r="G22" s="1"/>
+        <v>1</v>
+      </c>
+      <c r="F22" s="1">
+        <v>56.59</v>
+      </c>
+      <c r="G22" s="1" t="s">
+        <v>109</v>
+      </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" s="1">
-        <v>115456</v>
+        <v>132858</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>43</v>
+        <v>23</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="D23" s="2" t="s">
         <v>2</v>
       </c>
       <c r="E23" s="1">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F23" s="1">
-        <v>23.99</v>
+        <v>299.99</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>44</v>
+        <v>110</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" s="1">
-        <v>115601</v>
+        <v>132907</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>45</v>
+        <v>25</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>46</v>
+        <v>1</v>
       </c>
       <c r="D24" s="2" t="s">
         <v>2</v>
@@ -1402,22 +1356,18 @@
       <c r="E24" s="1">
         <v>1</v>
       </c>
-      <c r="F24" s="1">
-        <v>39.49</v>
-      </c>
-      <c r="G24" s="1" t="s">
-        <v>47</v>
-      </c>
+      <c r="F24" s="1"/>
+      <c r="G24" s="1"/>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" s="1">
-        <v>115947</v>
+        <v>133161</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>48</v>
+        <v>26</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>2</v>
@@ -1426,224 +1376,216 @@
         <v>2</v>
       </c>
       <c r="F25" s="1">
-        <v>15.29</v>
+        <v>16.690000000000001</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>49</v>
+        <v>107</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" s="1">
-        <v>116449</v>
+        <v>134835</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>50</v>
+        <v>27</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>2</v>
       </c>
       <c r="E26" s="1">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="F26" s="1">
-        <v>2.5499999999999998</v>
+        <v>51.13</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>51</v>
+        <v>95</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" s="1">
-        <v>116456</v>
+        <v>136147</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>52</v>
+        <v>28</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="D27" s="2" t="s">
         <v>2</v>
       </c>
       <c r="E27" s="1">
-        <v>2</v>
-      </c>
-      <c r="F27" s="1">
-        <v>8.7899999999999991</v>
-      </c>
-      <c r="G27" s="1" t="s">
-        <v>21</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="F27" s="1"/>
+      <c r="G27" s="1"/>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" s="1">
-        <v>116461</v>
+        <v>137391</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>53</v>
+        <v>29</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="D28" s="2" t="s">
         <v>2</v>
       </c>
       <c r="E28" s="1">
-        <v>100</v>
-      </c>
-      <c r="F28" s="1">
-        <v>0.38</v>
-      </c>
-      <c r="G28" s="1" t="s">
-        <v>21</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="F28" s="1"/>
+      <c r="G28" s="1"/>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" s="1">
-        <v>116470</v>
+        <v>137480</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>54</v>
+        <v>30</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="D29" s="2" t="s">
         <v>2</v>
       </c>
       <c r="E29" s="1">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="F29" s="1">
-        <v>1.95</v>
+        <v>32.22</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>55</v>
+        <v>103</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" s="1">
-        <v>116634</v>
+        <v>141891</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>56</v>
+        <v>31</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>57</v>
+        <v>1</v>
       </c>
       <c r="D30" s="2" t="s">
         <v>2</v>
       </c>
       <c r="E30" s="1">
-        <v>1</v>
-      </c>
-      <c r="F30" s="1">
-        <v>59.99</v>
-      </c>
-      <c r="G30" s="1" t="s">
-        <v>58</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="F30" s="1"/>
+      <c r="G30" s="1"/>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" s="1">
-        <v>116849</v>
+        <v>142660</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>59</v>
+        <v>32</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="D31" s="2" t="s">
         <v>2</v>
       </c>
       <c r="E31" s="1">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="F31" s="1">
-        <v>3.59</v>
+        <v>4.99</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>60</v>
+        <v>94</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" s="1">
-        <v>116862</v>
+        <v>145597</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>61</v>
+        <v>33</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="D32" s="2" t="s">
         <v>2</v>
       </c>
       <c r="E32" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F32" s="1">
-        <v>306.44</v>
+        <v>56.89</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>25</v>
+        <v>92</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33" s="1">
-        <v>118111</v>
+        <v>146832</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>62</v>
+        <v>34</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="D33" s="2" t="s">
         <v>2</v>
       </c>
       <c r="E33" s="1">
-        <v>2</v>
-      </c>
-      <c r="F33" s="1"/>
-      <c r="G33" s="1"/>
+        <v>1</v>
+      </c>
+      <c r="F33" s="1">
+        <v>96.86</v>
+      </c>
+      <c r="G33" s="1" t="s">
+        <v>104</v>
+      </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34" s="1">
-        <v>119605</v>
+        <v>164004</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>63</v>
+        <v>35</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>64</v>
+        <v>1</v>
       </c>
       <c r="D34" s="2" t="s">
         <v>2</v>
       </c>
       <c r="E34" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F34" s="1">
-        <v>99.88</v>
+        <v>91.48</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>44</v>
+        <v>111</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35" s="1">
-        <v>119607</v>
+        <v>167357</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>65</v>
+        <v>36</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>64</v>
+        <v>1</v>
       </c>
       <c r="D35" s="2" t="s">
         <v>2</v>
@@ -1652,21 +1594,21 @@
         <v>2</v>
       </c>
       <c r="F35" s="1">
-        <v>99.88</v>
+        <v>10.49</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>66</v>
+        <v>112</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36" s="1">
-        <v>119936</v>
+        <v>173869</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>67</v>
+        <v>37</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="D36" s="2" t="s">
         <v>2</v>
@@ -1675,44 +1617,40 @@
         <v>1</v>
       </c>
       <c r="F36" s="1">
-        <v>71.22</v>
+        <v>22.58</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>23</v>
+        <v>113</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37" s="1">
-        <v>120263</v>
+        <v>180520</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>68</v>
+        <v>38</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D37" s="2" t="s">
         <v>2</v>
       </c>
       <c r="E37" s="1">
-        <v>3</v>
-      </c>
-      <c r="F37" s="1">
-        <v>29.99</v>
-      </c>
-      <c r="G37" s="1" t="s">
-        <v>18</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="F37" s="1"/>
+      <c r="G37" s="1"/>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38" s="1">
-        <v>131490</v>
+        <v>184187</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>69</v>
+        <v>39</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>2</v>
@@ -1721,352 +1659,342 @@
         <v>1</v>
       </c>
       <c r="F38" s="1">
-        <v>60.11</v>
+        <v>7.19</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>70</v>
+        <v>93</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39" s="1">
-        <v>131893</v>
+        <v>184617</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>71</v>
+        <v>40</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D39" s="2" t="s">
         <v>2</v>
       </c>
       <c r="E39" s="1">
-        <v>6</v>
-      </c>
-      <c r="F39" s="1">
-        <v>8.44</v>
-      </c>
-      <c r="G39" s="1" t="s">
-        <v>6</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="F39" s="1"/>
+      <c r="G39" s="1"/>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40" s="1">
-        <v>131915</v>
+        <v>192126</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>72</v>
+        <v>41</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="D40" s="2" t="s">
         <v>2</v>
       </c>
       <c r="E40" s="1">
-        <v>7</v>
-      </c>
-      <c r="F40" s="1">
-        <v>11.88</v>
-      </c>
-      <c r="G40" s="1" t="s">
-        <v>21</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="F40" s="1"/>
+      <c r="G40" s="1"/>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41" s="1">
-        <v>131918</v>
+        <v>192401</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>73</v>
+        <v>42</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="D41" s="2" t="s">
         <v>2</v>
       </c>
       <c r="E41" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F41" s="1">
-        <v>9.26</v>
+        <v>14.64</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>21</v>
+        <v>94</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42" s="1">
-        <v>132907</v>
+        <v>198048</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>74</v>
+        <v>43</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>12</v>
+        <v>44</v>
       </c>
       <c r="D42" s="2" t="s">
         <v>2</v>
       </c>
       <c r="E42" s="1">
-        <v>2</v>
-      </c>
-      <c r="F42" s="1"/>
-      <c r="G42" s="1"/>
+        <v>4</v>
+      </c>
+      <c r="F42" s="1">
+        <v>13.29</v>
+      </c>
+      <c r="G42" s="1" t="s">
+        <v>109</v>
+      </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43" s="1">
-        <v>133386</v>
+        <v>203543</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>75</v>
+        <v>45</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="D43" s="2" t="s">
         <v>2</v>
       </c>
       <c r="E43" s="1">
-        <v>3</v>
-      </c>
-      <c r="F43" s="1">
-        <v>21.89</v>
-      </c>
-      <c r="G43" s="1" t="s">
-        <v>60</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="F43" s="1"/>
+      <c r="G43" s="1"/>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44" s="1">
-        <v>139784</v>
+        <v>206386</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>76</v>
+        <v>46</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="D44" s="2" t="s">
         <v>2</v>
       </c>
       <c r="E44" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F44" s="1">
-        <v>339.81</v>
+        <v>127.44</v>
       </c>
       <c r="G44" s="1" t="s">
-        <v>77</v>
+        <v>114</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45" s="1">
-        <v>140806</v>
+        <v>209705</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>78</v>
+        <v>47</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D45" s="2" t="s">
         <v>2</v>
       </c>
       <c r="E45" s="1">
-        <v>10</v>
-      </c>
-      <c r="F45" s="1"/>
-      <c r="G45" s="1"/>
+        <v>1</v>
+      </c>
+      <c r="F45" s="1">
+        <v>1538.11</v>
+      </c>
+      <c r="G45" s="1" t="s">
+        <v>115</v>
+      </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A46" s="1">
-        <v>141891</v>
+        <v>212579</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>79</v>
+        <v>48</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>12</v>
+        <v>49</v>
       </c>
       <c r="D46" s="2" t="s">
         <v>2</v>
       </c>
       <c r="E46" s="1">
-        <v>4</v>
-      </c>
-      <c r="F46" s="1">
-        <v>0.38</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="F46" s="1"/>
       <c r="G46" s="1"/>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47" s="1">
-        <v>143272</v>
+        <v>214696</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>12</v>
+        <v>49</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>81</v>
+        <v>2</v>
       </c>
       <c r="E47" s="1">
-        <v>70</v>
+        <v>10</v>
       </c>
       <c r="F47" s="1">
-        <v>215.11</v>
+        <v>1.22</v>
       </c>
       <c r="G47" s="1" t="s">
-        <v>82</v>
+        <v>96</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48" s="1">
-        <v>143704</v>
+        <v>215088</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>83</v>
+        <v>51</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>12</v>
+        <v>49</v>
       </c>
       <c r="D48" s="2" t="s">
         <v>2</v>
       </c>
       <c r="E48" s="1">
-        <v>20</v>
-      </c>
-      <c r="F48" s="1">
-        <v>0.87</v>
-      </c>
-      <c r="G48" s="1" t="s">
-        <v>21</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="F48" s="1"/>
+      <c r="G48" s="1"/>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A49" s="1">
-        <v>145431</v>
+        <v>215187</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>84</v>
+        <v>52</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>12</v>
+        <v>49</v>
       </c>
       <c r="D49" s="2" t="s">
         <v>2</v>
       </c>
       <c r="E49" s="1">
-        <v>70</v>
+        <v>2</v>
       </c>
       <c r="F49" s="1">
-        <v>11.45</v>
+        <v>69.989999999999995</v>
       </c>
       <c r="G49" s="1" t="s">
-        <v>21</v>
+        <v>107</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A50" s="1">
-        <v>146832</v>
+        <v>215250</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>85</v>
+        <v>53</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>12</v>
+        <v>49</v>
       </c>
       <c r="D50" s="2" t="s">
         <v>2</v>
       </c>
       <c r="E50" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F50" s="1">
-        <v>120.11</v>
+        <v>199.88</v>
       </c>
       <c r="G50" s="1" t="s">
-        <v>86</v>
+        <v>116</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A51" s="1">
-        <v>152501</v>
+        <v>215321</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>87</v>
+        <v>54</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>12</v>
+        <v>49</v>
       </c>
       <c r="D51" s="2" t="s">
         <v>2</v>
       </c>
       <c r="E51" s="1">
-        <v>1</v>
-      </c>
-      <c r="F51" s="1"/>
-      <c r="G51" s="1"/>
+        <v>2</v>
+      </c>
+      <c r="F51" s="1">
+        <v>12.23</v>
+      </c>
+      <c r="G51" s="1" t="s">
+        <v>117</v>
+      </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A52" s="1">
-        <v>155730</v>
+        <v>215348</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>88</v>
+        <v>55</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>12</v>
+        <v>49</v>
       </c>
       <c r="D52" s="2" t="s">
         <v>2</v>
       </c>
       <c r="E52" s="1">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="F52" s="1">
-        <v>1473</v>
+        <v>58.44</v>
       </c>
       <c r="G52" s="1" t="s">
-        <v>9</v>
+        <v>118</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A53" s="1">
-        <v>156595</v>
+        <v>215350</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>89</v>
+        <v>56</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>12</v>
+        <v>49</v>
       </c>
       <c r="D53" s="2" t="s">
         <v>2</v>
       </c>
       <c r="E53" s="1">
-        <v>2</v>
-      </c>
-      <c r="F53" s="1">
-        <v>69.44</v>
-      </c>
-      <c r="G53" s="1" t="s">
-        <v>90</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="F53" s="1"/>
+      <c r="G53" s="1"/>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A54" s="1">
-        <v>159802</v>
+        <v>215382</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>91</v>
+        <v>57</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>92</v>
+        <v>49</v>
       </c>
       <c r="D54" s="2" t="s">
         <v>2</v>
@@ -2074,87 +2002,91 @@
       <c r="E54" s="1">
         <v>10</v>
       </c>
-      <c r="F54" s="1"/>
-      <c r="G54" s="1"/>
+      <c r="F54" s="1">
+        <v>54.46</v>
+      </c>
+      <c r="G54" s="1" t="s">
+        <v>118</v>
+      </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A55" s="1">
-        <v>161587</v>
+        <v>215395</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>93</v>
+        <v>58</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>12</v>
+        <v>49</v>
       </c>
       <c r="D55" s="2" t="s">
         <v>2</v>
       </c>
       <c r="E55" s="1">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="F55" s="1">
-        <v>53.11</v>
+        <v>16.18</v>
       </c>
       <c r="G55" s="1" t="s">
-        <v>90</v>
+        <v>119</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A56" s="1">
-        <v>164004</v>
+        <v>215457</v>
       </c>
       <c r="B56" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E56" s="1">
+        <v>4</v>
+      </c>
+      <c r="F56" s="1">
+        <v>20.190000000000001</v>
+      </c>
+      <c r="G56" s="1" t="s">
         <v>94</v>
-      </c>
-      <c r="C56" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D56" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="E56" s="1">
-        <v>2</v>
-      </c>
-      <c r="F56" s="1">
-        <v>89.88</v>
-      </c>
-      <c r="G56" s="1" t="s">
-        <v>95</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A57" s="1">
-        <v>166917</v>
+        <v>215465</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>96</v>
+        <v>60</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>97</v>
+        <v>49</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>2</v>
+        <v>61</v>
       </c>
       <c r="E57" s="1">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F57" s="1">
-        <v>14.77</v>
+        <v>17.489999999999998</v>
       </c>
       <c r="G57" s="1" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A58" s="1">
-        <v>167357</v>
+        <v>215473</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>99</v>
+        <v>62</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>12</v>
+        <v>49</v>
       </c>
       <c r="D58" s="2" t="s">
         <v>2</v>
@@ -2162,150 +2094,144 @@
       <c r="E58" s="1">
         <v>2</v>
       </c>
-      <c r="F58" s="1">
-        <v>10.99</v>
-      </c>
-      <c r="G58" s="1" t="s">
-        <v>44</v>
-      </c>
+      <c r="F58" s="1"/>
+      <c r="G58" s="1"/>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A59" s="1">
-        <v>173558</v>
+        <v>215478</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>100</v>
+        <v>63</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>12</v>
+        <v>49</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>2</v>
+        <v>61</v>
       </c>
       <c r="E59" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F59" s="1">
-        <v>11.99</v>
+        <v>23.89</v>
       </c>
       <c r="G59" s="1" t="s">
-        <v>32</v>
+        <v>94</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A60" s="1">
-        <v>174391</v>
+        <v>215487</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>101</v>
+        <v>64</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>12</v>
+        <v>49</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>2</v>
+        <v>61</v>
       </c>
       <c r="E60" s="1">
         <v>10</v>
       </c>
-      <c r="F60" s="1">
-        <v>17.989999999999998</v>
-      </c>
-      <c r="G60" s="1" t="s">
-        <v>23</v>
-      </c>
+      <c r="F60" s="1"/>
+      <c r="G60" s="1"/>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A61" s="1">
-        <v>174692</v>
+        <v>215489</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>102</v>
+        <v>65</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>12</v>
+        <v>49</v>
       </c>
       <c r="D61" s="2" t="s">
         <v>2</v>
       </c>
       <c r="E61" s="1">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F61" s="1">
-        <v>125.99</v>
+        <v>185.25</v>
       </c>
       <c r="G61" s="1" t="s">
-        <v>21</v>
+        <v>95</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A62" s="1">
-        <v>176002</v>
+        <v>215490</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>103</v>
+        <v>66</v>
       </c>
       <c r="C62" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="D62" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E62" s="1">
         <v>5</v>
-      </c>
-      <c r="D62" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="E62" s="1">
-        <v>20</v>
       </c>
       <c r="F62" s="1"/>
       <c r="G62" s="1"/>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A63" s="1">
-        <v>184617</v>
+        <v>215515</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>104</v>
+        <v>67</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>12</v>
+        <v>49</v>
       </c>
       <c r="D63" s="2" t="s">
         <v>2</v>
       </c>
       <c r="E63" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F63" s="1"/>
       <c r="G63" s="1"/>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A64" s="1">
-        <v>189300</v>
+        <v>215519</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>105</v>
+        <v>68</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>12</v>
+        <v>49</v>
       </c>
       <c r="D64" s="2" t="s">
         <v>2</v>
       </c>
       <c r="E64" s="1">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F64" s="1">
-        <v>11.69</v>
-      </c>
-      <c r="G64" s="1"/>
+        <v>7.94</v>
+      </c>
+      <c r="G64" s="1" t="s">
+        <v>94</v>
+      </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A65" s="1">
-        <v>191754</v>
+        <v>215520</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>106</v>
+        <v>69</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>12</v>
+        <v>49</v>
       </c>
       <c r="D65" s="2" t="s">
         <v>2</v>
@@ -2314,38 +2240,44 @@
         <v>5</v>
       </c>
       <c r="F65" s="1">
-        <v>11.69</v>
-      </c>
-      <c r="G65" s="1"/>
+        <v>6.39</v>
+      </c>
+      <c r="G65" s="1" t="s">
+        <v>94</v>
+      </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A66" s="1">
-        <v>198242</v>
+        <v>215527</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>107</v>
+        <v>70</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>12</v>
+        <v>49</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>2</v>
+        <v>61</v>
       </c>
       <c r="E66" s="1">
-        <v>1</v>
-      </c>
-      <c r="F66" s="1"/>
-      <c r="G66" s="1"/>
+        <v>6</v>
+      </c>
+      <c r="F66" s="1">
+        <v>11.16</v>
+      </c>
+      <c r="G66" s="1" t="s">
+        <v>94</v>
+      </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A67" s="1">
-        <v>206386</v>
+        <v>215536</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>108</v>
+        <v>71</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>12</v>
+        <v>49</v>
       </c>
       <c r="D67" s="2" t="s">
         <v>2</v>
@@ -2354,472 +2286,357 @@
         <v>2</v>
       </c>
       <c r="F67" s="1">
-        <v>126.22</v>
+        <v>14.77</v>
       </c>
       <c r="G67" s="1" t="s">
-        <v>109</v>
+        <v>94</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A68" s="1">
-        <v>214707</v>
+        <v>215544</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>110</v>
+        <v>72</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>111</v>
+        <v>49</v>
       </c>
       <c r="D68" s="2" t="s">
         <v>2</v>
       </c>
       <c r="E68" s="1">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F68" s="1"/>
       <c r="G68" s="1"/>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A69" s="1">
-        <v>215169</v>
+        <v>215551</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>112</v>
+        <v>73</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>12</v>
+        <v>49</v>
       </c>
       <c r="D69" s="2" t="s">
         <v>2</v>
       </c>
       <c r="E69" s="1">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F69" s="1">
-        <v>74.489999999999995</v>
+        <v>5.99</v>
       </c>
       <c r="G69" s="1" t="s">
-        <v>113</v>
+        <v>94</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A70" s="1">
-        <v>215228</v>
+        <v>217143</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>114</v>
+        <v>74</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>111</v>
+        <v>1</v>
       </c>
       <c r="D70" s="2" t="s">
         <v>2</v>
       </c>
       <c r="E70" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F70" s="1">
-        <v>191.55</v>
+        <v>117.22</v>
       </c>
       <c r="G70" s="1" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A71" s="1">
-        <v>215250</v>
+        <v>217247</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>116</v>
+        <v>75</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>111</v>
+        <v>49</v>
       </c>
       <c r="D71" s="2" t="s">
         <v>2</v>
       </c>
       <c r="E71" s="1">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F71" s="1">
-        <v>199.88</v>
+        <v>6.09</v>
       </c>
       <c r="G71" s="1" t="s">
-        <v>115</v>
+        <v>94</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A72" s="1">
-        <v>215321</v>
+        <v>217249</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>117</v>
+        <v>27</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>111</v>
+        <v>76</v>
       </c>
       <c r="D72" s="2" t="s">
         <v>2</v>
       </c>
       <c r="E72" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F72" s="1">
-        <v>12.23</v>
+        <v>51.48</v>
       </c>
       <c r="G72" s="1" t="s">
-        <v>118</v>
+        <v>95</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A73" s="1">
-        <v>215461</v>
+        <v>217326</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>119</v>
+        <v>77</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>111</v>
+        <v>1</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>81</v>
+        <v>2</v>
       </c>
       <c r="E73" s="1">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="F73" s="1">
-        <v>5.48</v>
+        <v>100.01</v>
       </c>
       <c r="G73" s="1" t="s">
-        <v>60</v>
+        <v>121</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A74" s="1">
-        <v>215490</v>
+        <v>217327</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>120</v>
+        <v>78</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>111</v>
+        <v>1</v>
       </c>
       <c r="D74" s="2" t="s">
         <v>2</v>
       </c>
       <c r="E74" s="1">
-        <v>5</v>
-      </c>
-      <c r="F74" s="1"/>
-      <c r="G74" s="1"/>
+        <v>10</v>
+      </c>
+      <c r="F74" s="1">
+        <v>66.150000000000006</v>
+      </c>
+      <c r="G74" s="1" t="s">
+        <v>122</v>
+      </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A75" s="1">
-        <v>215515</v>
+        <v>217753</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>121</v>
+        <v>79</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>111</v>
+        <v>49</v>
       </c>
       <c r="D75" s="2" t="s">
         <v>2</v>
       </c>
       <c r="E75" s="1">
-        <v>5</v>
-      </c>
-      <c r="F75" s="1"/>
+        <v>100</v>
+      </c>
+      <c r="F75" s="1">
+        <v>19.29</v>
+      </c>
       <c r="G75" s="1"/>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A76" s="1">
-        <v>215518</v>
+        <v>217827</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>122</v>
+        <v>80</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>111</v>
+        <v>49</v>
       </c>
       <c r="D76" s="2" t="s">
         <v>2</v>
       </c>
       <c r="E76" s="1">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F76" s="1">
-        <v>11.73</v>
+        <v>7.62</v>
       </c>
       <c r="G76" s="1" t="s">
-        <v>60</v>
+        <v>94</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A77" s="1">
-        <v>215527</v>
+        <v>217832</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>123</v>
+        <v>81</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>111</v>
+        <v>49</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>81</v>
+        <v>2</v>
       </c>
       <c r="E77" s="1">
-        <v>5</v>
-      </c>
-      <c r="F77" s="1">
-        <v>9.4600000000000009</v>
-      </c>
-      <c r="G77" s="1" t="s">
-        <v>60</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="F77" s="1"/>
+      <c r="G77" s="1"/>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A78" s="1">
-        <v>215533</v>
+        <v>217865</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>124</v>
+        <v>82</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>111</v>
+        <v>49</v>
       </c>
       <c r="D78" s="2" t="s">
         <v>2</v>
       </c>
       <c r="E78" s="1">
-        <v>6</v>
-      </c>
-      <c r="F78" s="1">
-        <v>3.59</v>
-      </c>
-      <c r="G78" s="1" t="s">
-        <v>60</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="F78" s="1"/>
+      <c r="G78" s="1"/>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A79" s="1">
-        <v>215540</v>
+        <v>217866</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>125</v>
+        <v>83</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>111</v>
+        <v>49</v>
       </c>
       <c r="D79" s="2" t="s">
         <v>2</v>
       </c>
       <c r="E79" s="1">
-        <v>7</v>
-      </c>
-      <c r="F79" s="1">
-        <v>21.19</v>
-      </c>
-      <c r="G79" s="1" t="s">
-        <v>60</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="F79" s="1"/>
+      <c r="G79" s="1"/>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A80" s="1">
-        <v>215544</v>
+        <v>217949</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>126</v>
+        <v>84</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>111</v>
+        <v>1</v>
       </c>
       <c r="D80" s="2" t="s">
         <v>2</v>
       </c>
       <c r="E80" s="1">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F80" s="1"/>
       <c r="G80" s="1"/>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A81" s="1">
-        <v>215551</v>
+        <v>218123</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>127</v>
+        <v>85</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>111</v>
+        <v>1</v>
       </c>
       <c r="D81" s="2" t="s">
         <v>2</v>
       </c>
       <c r="E81" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F81" s="1">
-        <v>5.99</v>
+        <v>7.51</v>
       </c>
       <c r="G81" s="1" t="s">
-        <v>60</v>
+        <v>94</v>
       </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A82" s="1">
-        <v>217143</v>
+        <v>218692</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>128</v>
+        <v>86</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>12</v>
+        <v>87</v>
       </c>
       <c r="D82" s="2" t="s">
         <v>2</v>
       </c>
       <c r="E82" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F82" s="1">
-        <v>117.22</v>
+        <v>181.22</v>
       </c>
       <c r="G82" s="1" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A83" s="1">
-        <v>217249</v>
+        <v>218739</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>130</v>
+        <v>88</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>46</v>
+        <v>1</v>
       </c>
       <c r="D83" s="2" t="s">
         <v>2</v>
       </c>
       <c r="E83" s="1">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F83" s="1">
-        <v>51.13</v>
+        <v>12.88</v>
       </c>
       <c r="G83" s="1" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A84" s="1">
-        <v>217308</v>
-      </c>
-      <c r="B84" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="C84" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D84" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="E84" s="1">
-        <v>20</v>
-      </c>
-      <c r="F84" s="1">
-        <v>181.11</v>
-      </c>
-      <c r="G84" s="1" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A85" s="1">
-        <v>217949</v>
-      </c>
-      <c r="B85" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="C85" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D85" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="E85" s="1">
-        <v>2</v>
-      </c>
-      <c r="F85" s="1"/>
-      <c r="G85" s="1"/>
-    </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A86" s="1">
-        <v>218123</v>
-      </c>
-      <c r="B86" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="C86" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D86" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="E86" s="1">
-        <v>5</v>
-      </c>
-      <c r="F86" s="1">
-        <v>7.49</v>
-      </c>
-      <c r="G86" s="1" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A87" s="1">
-        <v>218692</v>
-      </c>
-      <c r="B87" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="C87" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="D87" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="E87" s="1">
-        <v>1</v>
-      </c>
-      <c r="F87" s="1">
-        <v>179.44</v>
-      </c>
-      <c r="G87" s="1" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="88" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A88" s="1">
-        <v>220483</v>
-      </c>
-      <c r="B88" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="C88" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="D88" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="E88" s="1">
-        <v>5</v>
-      </c>
-      <c r="F88" s="1">
-        <v>31.55</v>
-      </c>
-      <c r="G88" s="1"/>
+        <v>124</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
